--- a/sheets/조재수대금교본/검수/달묘전설.xlsx
+++ b/sheets/조재수대금교본/검수/달묘전설.xlsx
@@ -2393,8 +2393,7 @@
         <is>
           <t xml:space="preserve">淋
 △
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="C4" s="23"/>
@@ -2402,8 +2401,7 @@
         <is>
           <t xml:space="preserve">淋
 △
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -2497,8 +2495,7 @@
         <is>
           <t xml:space="preserve">汰
 △
-汰㴌
-‹</t>
+汰㴌</t>
         </is>
       </c>
       <c r="C6" s="24"/>
@@ -2506,8 +2503,7 @@
         <is>
           <t xml:space="preserve">汰
 △
-湳㶐
-‹</t>
+湳㶐</t>
         </is>
       </c>
       <c r="E6" s="24"/>
@@ -2515,8 +2511,7 @@
         <is>
           <t xml:space="preserve">林
 –
-太姑
-‹</t>
+太姑</t>
         </is>
       </c>
       <c r="G6" s="24"/>
@@ -2524,8 +2519,7 @@
         <is>
           <t xml:space="preserve">林
 –
-仲林
-‹</t>
+仲林</t>
         </is>
       </c>
       <c r="I6" s="24"/>
@@ -2533,8 +2527,7 @@
         <is>
           <t xml:space="preserve">太
 –
-太姑
-‹</t>
+太姑</t>
         </is>
       </c>
       <c r="K6" s="24"/>
@@ -2542,8 +2535,7 @@
         <is>
           <t xml:space="preserve">太
 –
-南應
-‹</t>
+南應</t>
         </is>
       </c>
       <c r="M6" s="24"/>
@@ -2560,9 +2552,7 @@
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧
-–
-∧</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E7" s="22"/>
@@ -2699,24 +2689,15 @@
         </is>
       </c>
       <c r="C10" s="24"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="24"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="24"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –
-仲林
-‹</t>
+仲林</t>
         </is>
       </c>
       <c r="I10" s="24"/>
@@ -2724,8 +2705,7 @@
         <is>
           <t xml:space="preserve">–
 –
-仲林
-‹</t>
+仲林</t>
         </is>
       </c>
       <c r="K10" s="24"/>

--- a/sheets/조재수대금교본/검수/달묘전설.xlsx
+++ b/sheets/조재수대금교본/검수/달묘전설.xlsx
@@ -2552,7 +2552,9 @@
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">∧
+–
+∧</t>
         </is>
       </c>
       <c r="E7" s="22"/>

--- a/sheets/조재수대금교본/검수/달묘전설.xlsx
+++ b/sheets/조재수대금교본/검수/달묘전설.xlsx
@@ -2300,24 +2300,24 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="52.63" customHeight="true">
+    <row r="2" ht="48.19" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="117.4" customHeight="true">
+    <row r="3" ht="107.43" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="117.4" customHeight="true">
+    <row r="4" ht="107.43" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="117.4" customHeight="true">
+    <row r="5" ht="107.43" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="M5" s="23"/>
     </row>
-    <row r="6" ht="117.4" customHeight="true">
+    <row r="6" ht="107.43" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="M6" s="24"/>
     </row>
-    <row r="7" ht="117.4" customHeight="true">
+    <row r="7" ht="107.43" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" ht="117.4" customHeight="true">
+    <row r="8" ht="107.43" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="M8" s="23"/>
     </row>
-    <row r="9" ht="117.4" customHeight="true">
+    <row r="9" ht="107.43" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="M9" s="23"/>
     </row>
-    <row r="10" ht="117.4" customHeight="true">
+    <row r="10" ht="107.43" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2720,6 +2720,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="83"/>
 </worksheet>
 </file>